--- a/訂購單.xlsx
+++ b/訂購單.xlsx
@@ -63,7 +63,7 @@
       <name val="PingFang TC"/>
       <b val="1"/>
       <color rgb="00B23B12"/>
-      <sz val="11"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="PingFang TC"/>
@@ -540,10 +540,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" ht="38" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>【方案】原價 NT$1,190 → 線上優惠價 NT$490（解鎖全部教材＋嚕嚕安角色）</t>
+          <t>【方案】原價 NT$1,190 → 線上優惠價 NT$490（解鎖：自己上傳的譜無限暢玩＋全部嚕嚕安教材＋嚕嚕安角色）</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="24" customHeight="1">
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>銀行 / 代號</t>
@@ -629,13 +629,13 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>（請老師填入，例：822 中國信託）</t>
+          <t>822　中國信託</t>
         </is>
       </c>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="24" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>戶名</t>
@@ -643,13 +643,13 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>（請老師填入）</t>
+          <t>曾彥淳</t>
         </is>
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>匯款帳號</t>
@@ -657,7 +657,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>（請老師填入完整帳號）</t>
+          <t>509540203457</t>
         </is>
       </c>
       <c r="D17" s="7" t="n"/>
@@ -680,7 +680,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>2. 依②的帳號匯款 NT$490。</t>
+          <t>2. 依②的帳號匯款 NT$490（822 中國信託 · 曾彥淳 · 509540203457）。</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>5. 打開遊戲 → 在上方輸入解鎖密碼 → 全部教材與嚕嚕安角色立即解鎖 🎉</t>
+          <t>5. 打開遊戲 → 在上方輸入解鎖密碼 → 自己上傳的譜無限使用、全部教材與嚕嚕安角色立即解鎖 🎉</t>
         </is>
       </c>
     </row>
